--- a/docs/Role_Matrix.xlsx
+++ b/docs/Role_Matrix.xlsx
@@ -1,117 +1,64 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0c1aa8a78197503d/Documents/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="48" documentId="8_{A04CBF76-1DCC-400B-B2E1-57DD516963D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1B3F730A-95A8-48DC-A880-D2ABC214A36C}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{15461E8B-02B0-4143-8CC8-3077671F7151}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="14">
-  <si>
-    <t>Feature</t>
-  </si>
-  <si>
-    <t>User</t>
-  </si>
-  <si>
-    <t>TL</t>
-  </si>
-  <si>
-    <t>Manager</t>
-  </si>
-  <si>
-    <t>Admin</t>
-  </si>
-  <si>
-    <t>Super Admin</t>
-  </si>
-  <si>
-    <t>View Attendance</t>
-  </si>
-  <si>
-    <t>Edit Attendance</t>
-  </si>
-  <si>
-    <t>Apply Leave</t>
-  </si>
-  <si>
-    <t>Approve Leave</t>
-  </si>
-  <si>
-    <t>Assign Tasks</t>
-  </si>
-  <si>
-    <t>Generate Reports</t>
-  </si>
-  <si>
-    <t>Yes</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="5">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="8"/>
-      <color rgb="FF0D0D0D"/>
       <name val="Segoe UI"/>
       <family val="2"/>
+      <color rgb="FF0D0D0D"/>
+      <sz val="8"/>
     </font>
     <font>
-      <sz val="8"/>
-      <color rgb="FF0D0D0D"/>
       <name val="Segoe UI"/>
       <family val="2"/>
+      <color rgb="FF0D0D0D"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="10"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E7F7"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -119,28 +66,107 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00B7C3D0"/>
+      </left>
+      <right style="thin">
+        <color rgb="00B7C3D0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B7C3D0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B7C3D0"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+  <cellXfs count="5">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -440,152 +466,376 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{386B2890-F5D3-43A1-88FB-29A387C9A929}">
-  <dimension ref="A1:F7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" t="s">
-        <v>12</v>
-      </c>
-      <c r="D6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D7" t="s">
-        <v>13</v>
-      </c>
-      <c r="E7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F7" t="s">
-        <v>12</v>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>TL</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Super Admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>View Attendance</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Edit Attendance Timing</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>View Attendance Timing</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Apply Leave</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Approve Leave</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Assign Tasks</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Create User</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Create Team</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Generate Reports</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Manage Payroll Base Salary</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait"/>
 </worksheet>
 </file>